--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.138.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.138.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.138.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.138.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="49" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -605,19 +605,23 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN, U+00A4 CURRENCY SIGN | isolated marker/symbol line :: è¢¤</t>
+          <t>L7: stray/suspicious non-ASCII glyph(s): U+88A4 CJK UNIFIED IDEOGRAPH-88A4 | isolated marker/symbol line :: 袤</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: By a person entitled to haveâ€™a new trustee appointed</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDFRS OF JANUARY 1851.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDFRS OF JANUARY 1851.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN, U+00A4 CURRENCY SIGN | isolated marker/symbol line :: è¢¤</t>
+          <t>L7: stray/suspicious non-ASCII glyph(s): U+88A4 CJK UNIFIED IDEOGRAPH-88A4 | isolated marker/symbol line :: 袤</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
@@ -665,7 +669,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -680,14 +684,10 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Order. One is a â€œclaimâ€� for spec</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” ; and</t>
-        </is>
-      </c>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: -； and</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -745,16 +745,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: proceedings may be by " claim.â€� The</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” day of</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -770,7 +762,7 @@
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: f - -----â€”,</t>
+          <t>L99: punctuation artifact: double/multiple hyphen :: f - -----—,</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -794,12 +786,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -808,16 +800,8 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: er relief ; pray subpÃ¦na.)</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”except that the words referring to real assets of de- Within the</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -863,16 +847,8 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: claimâ€�for specific performance.</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: judgment creditors, as in the 6th articleâ€”with the addi- orders.</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -914,16 +890,8 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L121: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” except that the words referring to</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: f - -----â€”,</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -965,11 +933,7 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L127: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Ã¦ na.)</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
@@ -1012,11 +976,7 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L133: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: in the 6th articleâ€”with the addi-</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
@@ -1045,12 +1005,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1093,7 +1053,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
